--- a/lab2/lfsr_register_table.xlsx
+++ b/lab2/lfsr_register_table.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:AL53"/>
+  <dimension ref="B1:AL63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -653,25 +653,25 @@
         <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>1</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="6" t="n">
         <v>1</v>
@@ -683,67 +683,67 @@
         <v>0</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="T3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="V3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AE3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AG3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH3" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -757,25 +757,25 @@
         <v>1</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>1</v>
@@ -787,70 +787,70 @@
         <v>0</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB4" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AD4" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AF4" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AH4" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -861,25 +861,25 @@
         <v>1</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>1</v>
@@ -891,73 +891,73 @@
         <v>0</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AC5" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AE5" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AG5" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -965,25 +965,25 @@
         <v>3</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>1</v>
@@ -995,73 +995,73 @@
         <v>0</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AB6" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AD6" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AF6" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH6" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ6" s="7" t="n">
         <v>0</v>
@@ -1075,19 +1075,19 @@
         <v>1</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>1</v>
@@ -1099,79 +1099,79 @@
         <v>0</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AA7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AC7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AE7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1179,19 +1179,19 @@
         <v>5</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>1</v>
@@ -1203,79 +1203,79 @@
         <v>0</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Z8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AB8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AD8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" s="7" t="n">
         <v>0</v>
@@ -1289,13 +1289,13 @@
         <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1307,85 +1307,85 @@
         <v>0</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Y9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AA9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AC9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AH9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1393,13 +1393,13 @@
         <v>7</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>1</v>
@@ -1411,88 +1411,88 @@
         <v>0</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="X10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Z10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AB10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AG10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ10" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1503,7 +1503,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>1</v>
@@ -1515,91 +1515,91 @@
         <v>0</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Y11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AA11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AF11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AH11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ11" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1607,7 +1607,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>1</v>
@@ -1619,94 +1619,94 @@
         <v>0</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="X12" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Z12" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB12" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AE12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AG12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1723,97 +1723,97 @@
         <v>0</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Y13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AD13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AF13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ13" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1827,97 +1827,97 @@
         <v>0</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="X14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AC14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AE14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ14" s="7" t="n">
         <v>1</v>
@@ -1931,103 +1931,103 @@
         <v>0</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="U15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="W15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AB15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AD15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AJ15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2035,103 +2035,103 @@
         <v>13</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AA16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AC16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ16" s="7" t="n">
         <v>1</v>
@@ -2145,103 +2145,103 @@
         <v>0</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Z17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AB17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AH17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AJ17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2249,103 +2249,103 @@
         <v>15</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Y18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AA18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AG18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ18" s="7" t="n">
         <v>0</v>
@@ -2359,97 +2359,97 @@
         <v>0</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="X19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Z19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AF19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AH19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="6" t="n">
         <v>0</v>
@@ -2463,97 +2463,97 @@
         <v>17</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Y20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AE20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AG20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH20" s="6" t="n">
         <v>0</v>
@@ -2573,91 +2573,91 @@
         <v>0</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="X21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AD21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AF21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG21" s="6" t="n">
         <v>0</v>
@@ -2677,91 +2677,91 @@
         <v>19</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>1</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" s="6" t="n">
         <v>1</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB22" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AC22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD22" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AE22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF22" s="6" t="n">
         <v>0</v>
@@ -2784,88 +2784,88 @@
         <v>20</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>1</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" s="6" t="n">
         <v>1</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA23" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AB23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC23" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AD23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE23" s="6" t="n">
         <v>0</v>
@@ -2891,85 +2891,85 @@
         <v>21</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>1</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z24" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AA24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB24" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AC24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD24" s="6" t="n">
         <v>0</v>
@@ -2998,82 +2998,82 @@
         <v>22</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>1</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Z25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA25" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AB25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC25" s="6" t="n">
         <v>0</v>
@@ -3105,79 +3105,79 @@
         <v>23</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" s="6" t="n">
         <v>1</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X26" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Y26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AA26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB26" s="6" t="n">
         <v>0</v>
@@ -3212,76 +3212,76 @@
         <v>24</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="6" t="n">
         <v>1</v>
       </c>
       <c r="X27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y27" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Z27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA27" s="6" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
         <v>1</v>
       </c>
       <c r="AJ27" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -3319,73 +3319,73 @@
         <v>25</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="6" t="n">
         <v>1</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X28" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Y28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z28" s="6" t="n">
         <v>0</v>
@@ -3415,7 +3415,7 @@
         <v>1</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ28" s="7" t="n">
         <v>0</v>
@@ -3426,70 +3426,70 @@
         <v>26</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U29" s="6" t="n">
         <v>1</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W29" s="6" t="n">
         <v>1</v>
       </c>
       <c r="X29" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y29" s="6" t="n">
         <v>0</v>
@@ -3519,13 +3519,13 @@
         <v>1</v>
       </c>
       <c r="AH29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AJ29" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -3536,64 +3536,64 @@
         <v>1</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" s="6" t="n">
         <v>1</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="6" t="n">
         <v>1</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X30" s="6" t="n">
         <v>0</v>
@@ -3623,16 +3623,16 @@
         <v>1</v>
       </c>
       <c r="AG30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ30" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -3640,64 +3640,64 @@
         <v>28</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T31" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U31" s="6" t="n">
         <v>1</v>
       </c>
       <c r="V31" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W31" s="6" t="n">
         <v>0</v>
@@ -3727,19 +3727,19 @@
         <v>1</v>
       </c>
       <c r="AF31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AH31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ31" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3750,58 +3750,58 @@
         <v>1</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" s="6" t="n">
         <v>1</v>
       </c>
       <c r="S32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T32" s="6" t="n">
         <v>1</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" s="6" t="n">
         <v>0</v>
@@ -3831,19 +3831,19 @@
         <v>1</v>
       </c>
       <c r="AE32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AG32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ32" s="7" t="n">
         <v>1</v>
@@ -3854,58 +3854,58 @@
         <v>30</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>1</v>
       </c>
       <c r="R33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U33" s="6" t="n">
         <v>0</v>
@@ -3935,25 +3935,25 @@
         <v>1</v>
       </c>
       <c r="AD33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AF33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AJ33" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3964,52 +3964,52 @@
         <v>1</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P34" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" s="6" t="n">
         <v>1</v>
       </c>
       <c r="S34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T34" s="6" t="n">
         <v>0</v>
@@ -4039,25 +4039,25 @@
         <v>1</v>
       </c>
       <c r="AC34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AE34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH34" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AI34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ34" s="7" t="n">
         <v>1</v>
@@ -4068,52 +4068,52 @@
         <v>32</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" s="6" t="n">
         <v>1</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>1</v>
       </c>
       <c r="R35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" s="6" t="n">
         <v>0</v>
@@ -4143,31 +4143,31 @@
         <v>1</v>
       </c>
       <c r="AB35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AD35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG35" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AH35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AJ35" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -4175,49 +4175,49 @@
         <v>33</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Q36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" s="6" t="n">
         <v>0</v>
@@ -4247,34 +4247,34 @@
         <v>1</v>
       </c>
       <c r="AA36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AC36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AG36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AI36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ36" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -4282,46 +4282,46 @@
         <v>34</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" s="6" t="n">
         <v>1</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -4351,37 +4351,37 @@
         <v>1</v>
       </c>
       <c r="Z37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AB37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD37" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE37" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AF37" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG37" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AH37" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ37" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -4389,43 +4389,43 @@
         <v>35</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>1</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" s="6" t="n">
         <v>1</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P38" s="6" t="n">
         <v>0</v>
@@ -4455,40 +4455,40 @@
         <v>1</v>
       </c>
       <c r="Y38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AA38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD38" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AE38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF38" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AG38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ38" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -4499,37 +4499,37 @@
         <v>0</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>1</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" s="6" t="n">
         <v>0</v>
@@ -4559,40 +4559,40 @@
         <v>1</v>
       </c>
       <c r="X39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Z39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC39" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AD39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE39" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AF39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ39" s="7" t="n">
         <v>1</v>
@@ -4603,37 +4603,37 @@
         <v>37</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="6" t="n">
         <v>1</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" s="6" t="n">
         <v>0</v>
@@ -4663,40 +4663,40 @@
         <v>1</v>
       </c>
       <c r="W40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Y40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB40" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AC40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD40" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AE40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI40" s="6" t="n">
         <v>1</v>
@@ -4713,31 +4713,31 @@
         <v>0</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" s="6" t="n">
         <v>1</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" s="6" t="n">
         <v>0</v>
@@ -4767,40 +4767,40 @@
         <v>1</v>
       </c>
       <c r="V41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="X41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA41" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AB41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC41" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AD41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH41" s="6" t="n">
         <v>1</v>
@@ -4817,31 +4817,31 @@
         <v>39</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="6" t="n">
         <v>0</v>
@@ -4871,40 +4871,40 @@
         <v>1</v>
       </c>
       <c r="U42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="W42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z42" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AA42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB42" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AC42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG42" s="6" t="n">
         <v>1</v>
@@ -4924,28 +4924,28 @@
         <v>40</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" s="6" t="n">
         <v>0</v>
@@ -4975,40 +4975,40 @@
         <v>1</v>
       </c>
       <c r="T43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="V43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X43" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y43" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Z43" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA43" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AB43" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC43" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD43" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE43" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF43" s="6" t="n">
         <v>1</v>
@@ -5031,25 +5031,25 @@
         <v>41</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" s="6" t="n">
         <v>0</v>
@@ -5079,40 +5079,40 @@
         <v>1</v>
       </c>
       <c r="S44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="U44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W44" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X44" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Y44" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z44" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AA44" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB44" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC44" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD44" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE44" s="6" t="n">
         <v>1</v>
@@ -5138,22 +5138,22 @@
         <v>42</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>0</v>
@@ -5183,40 +5183,40 @@
         <v>1</v>
       </c>
       <c r="R45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="T45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W45" s="6" t="n">
         <v>1</v>
       </c>
       <c r="X45" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Z45" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA45" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB45" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC45" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD45" s="6" t="n">
         <v>1</v>
@@ -5237,7 +5237,7 @@
         <v>1</v>
       </c>
       <c r="AJ45" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -5245,19 +5245,19 @@
         <v>43</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
         <v>0</v>
@@ -5287,40 +5287,40 @@
         <v>1</v>
       </c>
       <c r="Q46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U46" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="6" t="n">
         <v>1</v>
       </c>
       <c r="W46" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X46" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Y46" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB46" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC46" s="6" t="n">
         <v>1</v>
@@ -5341,7 +5341,7 @@
         <v>1</v>
       </c>
       <c r="AI46" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ46" s="7" t="n">
         <v>1</v>
@@ -5355,13 +5355,13 @@
         <v>1</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>0</v>
@@ -5391,40 +5391,40 @@
         <v>1</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R47" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T47" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U47" s="6" t="n">
         <v>1</v>
       </c>
       <c r="V47" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W47" s="6" t="n">
         <v>1</v>
       </c>
       <c r="X47" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y47" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z47" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA47" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB47" s="6" t="n">
         <v>1</v>
@@ -5445,7 +5445,7 @@
         <v>1</v>
       </c>
       <c r="AH47" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="6" t="n">
         <v>1</v>
@@ -5459,13 +5459,13 @@
         <v>45</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>0</v>
@@ -5495,40 +5495,40 @@
         <v>1</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S48" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T48" s="6" t="n">
         <v>1</v>
       </c>
       <c r="U48" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V48" s="6" t="n">
         <v>1</v>
       </c>
       <c r="W48" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X48" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y48" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z48" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA48" s="6" t="n">
         <v>1</v>
@@ -5549,7 +5549,7 @@
         <v>1</v>
       </c>
       <c r="AG48" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH48" s="6" t="n">
         <v>1</v>
@@ -5569,7 +5569,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" s="6" t="n">
         <v>0</v>
@@ -5599,40 +5599,40 @@
         <v>1</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T49" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U49" s="6" t="n">
         <v>1</v>
       </c>
       <c r="V49" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W49" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X49" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y49" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z49" s="6" t="n">
         <v>1</v>
@@ -5653,7 +5653,7 @@
         <v>1</v>
       </c>
       <c r="AF49" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG49" s="6" t="n">
         <v>1</v>
@@ -5665,7 +5665,7 @@
         <v>0</v>
       </c>
       <c r="AJ49" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -5673,7 +5673,7 @@
         <v>47</v>
       </c>
       <c r="C50" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50" s="6" t="n">
         <v>0</v>
@@ -5703,40 +5703,40 @@
         <v>1</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q50" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R50" s="6" t="n">
         <v>1</v>
       </c>
       <c r="S50" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T50" s="6" t="n">
         <v>1</v>
       </c>
       <c r="U50" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V50" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W50" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X50" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y50" s="6" t="n">
         <v>1</v>
@@ -5757,7 +5757,7 @@
         <v>1</v>
       </c>
       <c r="AE50" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF50" s="6" t="n">
         <v>1</v>
@@ -5769,7 +5769,7 @@
         <v>0</v>
       </c>
       <c r="AI50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ50" s="7" t="n">
         <v>0</v>
@@ -5807,40 +5807,40 @@
         <v>1</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="6" t="n">
         <v>1</v>
       </c>
       <c r="R51" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T51" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U51" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V51" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W51" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X51" s="6" t="n">
         <v>1</v>
@@ -5861,7 +5861,7 @@
         <v>1</v>
       </c>
       <c r="AD51" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE51" s="6" t="n">
         <v>1</v>
@@ -5873,13 +5873,13 @@
         <v>0</v>
       </c>
       <c r="AH51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AJ51" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -5911,40 +5911,40 @@
         <v>1</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P52" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Q52" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52" s="6" t="n">
         <v>1</v>
       </c>
       <c r="S52" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T52" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U52" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V52" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W52" s="6" t="n">
         <v>1</v>
@@ -5965,7 +5965,7 @@
         <v>1</v>
       </c>
       <c r="AC52" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD52" s="6" t="n">
         <v>1</v>
@@ -5977,13 +5977,13 @@
         <v>0</v>
       </c>
       <c r="AG52" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AI52" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ52" s="7" t="n">
         <v>1</v>
@@ -6015,40 +6015,40 @@
         <v>1</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" s="6" t="n">
         <v>1</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q53" s="6" t="n">
         <v>1</v>
       </c>
       <c r="R53" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T53" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U53" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V53" s="6" t="n">
         <v>1</v>
@@ -6069,7 +6069,7 @@
         <v>1</v>
       </c>
       <c r="AB53" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC53" s="6" t="n">
         <v>1</v>
@@ -6081,19 +6081,1089 @@
         <v>0</v>
       </c>
       <c r="AF53" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG53" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AH53" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI53" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AJ53" s="7" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ55" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ56" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ57" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ58" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ59" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ60" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ61" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ62" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ63" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/lab2/lfsr_register_table.xlsx
+++ b/lab2/lfsr_register_table.xlsx
@@ -653,52 +653,52 @@
         <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>1</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" s="6" t="n">
         <v>1</v>
       </c>
       <c r="S3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" s="6" t="n">
         <v>1</v>
       </c>
       <c r="U3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" s="6" t="n">
         <v>1</v>
@@ -710,37 +710,37 @@
         <v>1</v>
       </c>
       <c r="Y3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD3" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AE3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AG3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH3" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AI3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ3" s="7" t="n">
         <v>0</v>
@@ -757,52 +757,52 @@
         <v>1</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="R4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" s="6" t="n">
         <v>1</v>
@@ -814,37 +814,37 @@
         <v>1</v>
       </c>
       <c r="X4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AD4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AF4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AH4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" s="6" t="n">
         <v>0</v>
@@ -861,52 +861,52 @@
         <v>1</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" s="6" t="n">
         <v>1</v>
@@ -918,37 +918,37 @@
         <v>1</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AC5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AE5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AG5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH5" s="6" t="n">
         <v>0</v>
@@ -957,7 +957,7 @@
         <v>0</v>
       </c>
       <c r="AJ5" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -965,52 +965,52 @@
         <v>3</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="R6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" s="6" t="n">
         <v>1</v>
@@ -1022,37 +1022,37 @@
         <v>1</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AB6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AD6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AF6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" s="6" t="n">
         <v>0</v>
@@ -1061,7 +1061,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" s="7" t="n">
         <v>0</v>
@@ -1075,46 +1075,46 @@
         <v>1</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="6" t="n">
         <v>1</v>
@@ -1126,37 +1126,37 @@
         <v>1</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AA7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AC7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AE7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" s="6" t="n">
         <v>0</v>
@@ -1165,13 +1165,13 @@
         <v>0</v>
       </c>
       <c r="AH7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1179,46 +1179,46 @@
         <v>5</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>1</v>
@@ -1230,37 +1230,37 @@
         <v>1</v>
       </c>
       <c r="T8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Z8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AB8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AD8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="6" t="n">
         <v>0</v>
@@ -1269,13 +1269,13 @@
         <v>0</v>
       </c>
       <c r="AG8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AI8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" s="7" t="n">
         <v>0</v>
@@ -1289,40 +1289,40 @@
         <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" s="6" t="n">
         <v>1</v>
@@ -1334,37 +1334,37 @@
         <v>1</v>
       </c>
       <c r="S9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Y9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AA9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AC9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD9" s="6" t="n">
         <v>0</v>
@@ -1373,19 +1373,19 @@
         <v>0</v>
       </c>
       <c r="AF9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AH9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1393,40 +1393,40 @@
         <v>7</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" s="6" t="n">
         <v>1</v>
@@ -1438,37 +1438,37 @@
         <v>1</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="X10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Z10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AB10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC10" s="6" t="n">
         <v>0</v>
@@ -1477,22 +1477,22 @@
         <v>0</v>
       </c>
       <c r="AE10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AG10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AI10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ10" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1503,34 +1503,34 @@
         <v>1</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
         <v>1</v>
@@ -1542,37 +1542,37 @@
         <v>1</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Y11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AA11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11" s="6" t="n">
         <v>0</v>
@@ -1581,25 +1581,25 @@
         <v>0</v>
       </c>
       <c r="AD11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AF11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AH11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1607,34 +1607,34 @@
         <v>9</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="6" t="n">
         <v>1</v>
@@ -1646,37 +1646,37 @@
         <v>1</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="X12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Z12" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA12" s="6" t="n">
         <v>0</v>
@@ -1685,28 +1685,28 @@
         <v>0</v>
       </c>
       <c r="AC12" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AE12" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AG12" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH12" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1717,28 +1717,28 @@
         <v>1</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="6" t="n">
         <v>1</v>
@@ -1750,37 +1750,37 @@
         <v>1</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Y13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" s="6" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>0</v>
       </c>
       <c r="AB13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AD13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AF13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1821,28 +1821,28 @@
         <v>11</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>1</v>
@@ -1854,37 +1854,37 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="X14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" s="6" t="n">
         <v>0</v>
@@ -1893,34 +1893,34 @@
         <v>0</v>
       </c>
       <c r="AA14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AC14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AE14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1928,25 +1928,25 @@
         <v>12</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>1</v>
@@ -1958,37 +1958,37 @@
         <v>1</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="U15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="W15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" s="6" t="n">
         <v>0</v>
@@ -1997,34 +1997,34 @@
         <v>0</v>
       </c>
       <c r="Z15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AB15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AD15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ15" s="7" t="n">
         <v>0</v>
@@ -2038,19 +2038,19 @@
         <v>1</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>1</v>
@@ -2062,37 +2062,37 @@
         <v>1</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" s="6" t="n">
         <v>0</v>
@@ -2101,34 +2101,34 @@
         <v>0</v>
       </c>
       <c r="Y16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AA16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AC16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="6" t="n">
         <v>0</v>
@@ -2142,19 +2142,19 @@
         <v>14</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>1</v>
@@ -2166,37 +2166,37 @@
         <v>1</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="6" t="n">
         <v>0</v>
@@ -2205,34 +2205,34 @@
         <v>0</v>
       </c>
       <c r="X17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Z17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AB17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH17" s="6" t="n">
         <v>0</v>
@@ -2241,7 +2241,7 @@
         <v>1</v>
       </c>
       <c r="AJ17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -2252,13 +2252,13 @@
         <v>1</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -2270,37 +2270,37 @@
         <v>1</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>0</v>
@@ -2309,34 +2309,34 @@
         <v>0</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Y18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AA18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG18" s="6" t="n">
         <v>0</v>
@@ -2345,10 +2345,10 @@
         <v>1</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ18" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2356,13 +2356,13 @@
         <v>16</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>1</v>
@@ -2374,37 +2374,37 @@
         <v>1</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" s="6" t="n">
         <v>0</v>
@@ -2413,34 +2413,34 @@
         <v>0</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="X19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Z19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF19" s="6" t="n">
         <v>0</v>
@@ -2449,13 +2449,13 @@
         <v>1</v>
       </c>
       <c r="AH19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ19" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2466,7 +2466,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>1</v>
@@ -2478,37 +2478,37 @@
         <v>1</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" s="6" t="n">
         <v>0</v>
@@ -2517,34 +2517,34 @@
         <v>0</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Y20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE20" s="6" t="n">
         <v>0</v>
@@ -2553,16 +2553,16 @@
         <v>1</v>
       </c>
       <c r="AG20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ20" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2570,7 +2570,7 @@
         <v>18</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>1</v>
@@ -2582,37 +2582,37 @@
         <v>1</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" s="6" t="n">
         <v>0</v>
@@ -2621,34 +2621,34 @@
         <v>0</v>
       </c>
       <c r="T21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="X21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD21" s="6" t="n">
         <v>0</v>
@@ -2657,19 +2657,19 @@
         <v>1</v>
       </c>
       <c r="AF21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ21" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2686,37 +2686,37 @@
         <v>1</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>1</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" s="6" t="n">
         <v>1</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2725,34 +2725,34 @@
         <v>0</v>
       </c>
       <c r="S22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC22" s="6" t="n">
         <v>0</v>
@@ -2761,22 +2761,22 @@
         <v>1</v>
       </c>
       <c r="AE22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ22" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2790,37 +2790,37 @@
         <v>1</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>1</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
         <v>1</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" s="6" t="n">
         <v>0</v>
@@ -2829,34 +2829,34 @@
         <v>0</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB23" s="6" t="n">
         <v>0</v>
@@ -2865,25 +2865,25 @@
         <v>1</v>
       </c>
       <c r="AD23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ23" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2894,37 +2894,37 @@
         <v>1</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>1</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" s="6" t="n">
         <v>0</v>
@@ -2933,34 +2933,34 @@
         <v>0</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="6" t="n">
         <v>0</v>
@@ -2969,28 +2969,28 @@
         <v>1</v>
       </c>
       <c r="AC24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ24" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2998,37 +2998,37 @@
         <v>22</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>1</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
         <v>0</v>
@@ -3037,34 +3037,34 @@
         <v>0</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="6" t="n">
         <v>0</v>
@@ -3073,28 +3073,28 @@
         <v>1</v>
       </c>
       <c r="AB25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ25" s="7" t="n">
         <v>1</v>
@@ -3105,34 +3105,34 @@
         <v>23</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="6" t="n">
         <v>1</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="6" t="n">
         <v>0</v>
@@ -3141,34 +3141,34 @@
         <v>0</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="6" t="n">
         <v>0</v>
@@ -3177,28 +3177,28 @@
         <v>1</v>
       </c>
       <c r="AA26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI26" s="6" t="n">
         <v>1</v>
@@ -3212,31 +3212,31 @@
         <v>24</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="6" t="n">
         <v>0</v>
@@ -3245,34 +3245,34 @@
         <v>0</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X27" s="6" t="n">
         <v>0</v>
@@ -3281,28 +3281,28 @@
         <v>1</v>
       </c>
       <c r="Z27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH27" s="6" t="n">
         <v>1</v>
@@ -3319,28 +3319,28 @@
         <v>25</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" s="6" t="n">
         <v>0</v>
@@ -3349,34 +3349,34 @@
         <v>0</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W28" s="6" t="n">
         <v>0</v>
@@ -3385,28 +3385,28 @@
         <v>1</v>
       </c>
       <c r="Y28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG28" s="6" t="n">
         <v>1</v>
@@ -3418,7 +3418,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -3426,25 +3426,25 @@
         <v>26</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" s="6" t="n">
         <v>0</v>
@@ -3453,34 +3453,34 @@
         <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T29" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="6" t="n">
         <v>0</v>
@@ -3489,28 +3489,28 @@
         <v>1</v>
       </c>
       <c r="X29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF29" s="6" t="n">
         <v>1</v>
@@ -3522,10 +3522,10 @@
         <v>1</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ29" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3536,19 +3536,19 @@
         <v>1</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
@@ -3557,34 +3557,34 @@
         <v>0</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T30" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U30" s="6" t="n">
         <v>0</v>
@@ -3593,28 +3593,28 @@
         <v>1</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE30" s="6" t="n">
         <v>1</v>
@@ -3626,13 +3626,13 @@
         <v>1</v>
       </c>
       <c r="AH30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ30" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -3640,19 +3640,19 @@
         <v>28</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="6" t="n">
         <v>0</v>
@@ -3661,34 +3661,34 @@
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T31" s="6" t="n">
         <v>0</v>
@@ -3697,28 +3697,28 @@
         <v>1</v>
       </c>
       <c r="V31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD31" s="6" t="n">
         <v>1</v>
@@ -3730,13 +3730,13 @@
         <v>1</v>
       </c>
       <c r="AG31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH31" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ31" s="7" t="n">
         <v>0</v>
@@ -3750,13 +3750,13 @@
         <v>1</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>0</v>
@@ -3765,34 +3765,34 @@
         <v>0</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" s="6" t="n">
         <v>0</v>
@@ -3801,28 +3801,28 @@
         <v>1</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC32" s="6" t="n">
         <v>1</v>
@@ -3834,19 +3834,19 @@
         <v>1</v>
       </c>
       <c r="AF32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AJ32" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3854,13 +3854,13 @@
         <v>30</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>0</v>
@@ -3869,34 +3869,34 @@
         <v>0</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" s="6" t="n">
         <v>0</v>
@@ -3905,28 +3905,28 @@
         <v>1</v>
       </c>
       <c r="T33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB33" s="6" t="n">
         <v>1</v>
@@ -3938,19 +3938,19 @@
         <v>1</v>
       </c>
       <c r="AE33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AI33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ33" s="7" t="n">
         <v>0</v>
@@ -3964,7 +3964,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="6" t="n">
         <v>0</v>
@@ -3973,34 +3973,34 @@
         <v>0</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -4009,28 +4009,28 @@
         <v>1</v>
       </c>
       <c r="S34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA34" s="6" t="n">
         <v>1</v>
@@ -4042,25 +4042,25 @@
         <v>1</v>
       </c>
       <c r="AD34" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AH34" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AJ34" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -4068,7 +4068,7 @@
         <v>32</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" s="6" t="n">
         <v>0</v>
@@ -4077,34 +4077,34 @@
         <v>0</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P35" s="6" t="n">
         <v>0</v>
@@ -4113,28 +4113,28 @@
         <v>1</v>
       </c>
       <c r="R35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z35" s="6" t="n">
         <v>1</v>
@@ -4146,25 +4146,25 @@
         <v>1</v>
       </c>
       <c r="AC35" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AG35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AI35" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ35" s="7" t="n">
         <v>0</v>
@@ -4181,34 +4181,34 @@
         <v>0</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" s="6" t="n">
         <v>0</v>
@@ -4217,28 +4217,28 @@
         <v>1</v>
       </c>
       <c r="Q36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36" s="6" t="n">
         <v>1</v>
@@ -4250,31 +4250,31 @@
         <v>1</v>
       </c>
       <c r="AB36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AF36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AH36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AJ36" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -4285,34 +4285,34 @@
         <v>0</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" s="6" t="n">
         <v>0</v>
@@ -4321,28 +4321,28 @@
         <v>1</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" s="6" t="n">
         <v>1</v>
@@ -4354,34 +4354,34 @@
         <v>1</v>
       </c>
       <c r="AA37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB37" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC37" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AE37" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AG37" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ37" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -4389,34 +4389,34 @@
         <v>35</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="6" t="n">
         <v>0</v>
@@ -4425,28 +4425,28 @@
         <v>1</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W38" s="6" t="n">
         <v>1</v>
@@ -4458,37 +4458,37 @@
         <v>1</v>
       </c>
       <c r="Z38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AD38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AF38" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AH38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI38" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ38" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -4499,28 +4499,28 @@
         <v>0</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>0</v>
@@ -4529,28 +4529,28 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" s="6" t="n">
         <v>1</v>
@@ -4562,37 +4562,37 @@
         <v>1</v>
       </c>
       <c r="Y39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AC39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AE39" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AG39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI39" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ39" s="7" t="n">
         <v>1</v>
@@ -4603,28 +4603,28 @@
         <v>37</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
@@ -4633,28 +4633,28 @@
         <v>1</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U40" s="6" t="n">
         <v>1</v>
@@ -4666,43 +4666,43 @@
         <v>1</v>
       </c>
       <c r="X40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AB40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AD40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AF40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI40" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AJ40" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -4713,22 +4713,22 @@
         <v>0</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="6" t="n">
         <v>0</v>
@@ -4737,28 +4737,28 @@
         <v>1</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T41" s="6" t="n">
         <v>1</v>
@@ -4770,46 +4770,46 @@
         <v>1</v>
       </c>
       <c r="W41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AA41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AC41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AE41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH41" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AI41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ41" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -4817,22 +4817,22 @@
         <v>39</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>0</v>
@@ -4841,28 +4841,28 @@
         <v>1</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" s="6" t="n">
         <v>1</v>
@@ -4874,46 +4874,46 @@
         <v>1</v>
       </c>
       <c r="V42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Z42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AB42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AD42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG42" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AH42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ42" s="7" t="n">
         <v>0</v>
@@ -4924,19 +4924,19 @@
         <v>40</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" s="6" t="n">
         <v>0</v>
@@ -4945,28 +4945,28 @@
         <v>1</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" s="6" t="n">
         <v>1</v>
@@ -4978,46 +4978,46 @@
         <v>1</v>
       </c>
       <c r="U43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W43" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Y43" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AA43" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AC43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF43" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AG43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI43" s="6" t="n">
         <v>0</v>
@@ -5031,16 +5031,16 @@
         <v>41</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>0</v>
@@ -5049,28 +5049,28 @@
         <v>1</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q44" s="6" t="n">
         <v>1</v>
@@ -5082,46 +5082,46 @@
         <v>1</v>
       </c>
       <c r="T44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U44" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="X44" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Z44" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AB44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE44" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AF44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH44" s="6" t="n">
         <v>0</v>
@@ -5130,7 +5130,7 @@
         <v>0</v>
       </c>
       <c r="AJ44" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -5138,13 +5138,13 @@
         <v>42</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>0</v>
@@ -5153,28 +5153,28 @@
         <v>1</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P45" s="6" t="n">
         <v>1</v>
@@ -5186,46 +5186,46 @@
         <v>1</v>
       </c>
       <c r="S45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T45" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U45" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="W45" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Y45" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AA45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD45" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AE45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG45" s="6" t="n">
         <v>0</v>
@@ -5234,7 +5234,7 @@
         <v>0</v>
       </c>
       <c r="AI45" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ45" s="7" t="n">
         <v>0</v>
@@ -5245,10 +5245,10 @@
         <v>43</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" s="6" t="n">
         <v>0</v>
@@ -5257,28 +5257,28 @@
         <v>1</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46" s="6" t="n">
         <v>1</v>
@@ -5290,46 +5290,46 @@
         <v>1</v>
       </c>
       <c r="R46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T46" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="V46" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="X46" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Z46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC46" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AD46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF46" s="6" t="n">
         <v>0</v>
@@ -5338,13 +5338,13 @@
         <v>0</v>
       </c>
       <c r="AH46" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AJ46" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -5352,7 +5352,7 @@
         <v>44</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" s="6" t="n">
         <v>0</v>
@@ -5361,28 +5361,28 @@
         <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47" s="6" t="n">
         <v>1</v>
@@ -5394,46 +5394,46 @@
         <v>1</v>
       </c>
       <c r="Q47" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="U47" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="W47" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Y47" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z47" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA47" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB47" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AC47" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD47" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE47" s="6" t="n">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0</v>
       </c>
       <c r="AG47" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AI47" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ47" s="7" t="n">
         <v>0</v>
@@ -5465,28 +5465,28 @@
         <v>1</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="6" t="n">
         <v>1</v>
@@ -5498,46 +5498,46 @@
         <v>1</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="T48" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="V48" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="X48" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y48" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z48" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA48" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AB48" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC48" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD48" s="6" t="n">
         <v>0</v>
@@ -5546,13 +5546,13 @@
         <v>0</v>
       </c>
       <c r="AF48" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AH48" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI48" s="6" t="n">
         <v>0</v>
@@ -5569,28 +5569,28 @@
         <v>1</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="6" t="n">
         <v>1</v>
@@ -5602,46 +5602,46 @@
         <v>1</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S49" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="U49" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="W49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z49" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AA49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB49" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC49" s="6" t="n">
         <v>0</v>
@@ -5650,13 +5650,13 @@
         <v>0</v>
       </c>
       <c r="AE49" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AG49" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH49" s="6" t="n">
         <v>0</v>
@@ -5665,7 +5665,7 @@
         <v>0</v>
       </c>
       <c r="AJ49" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -5673,28 +5673,28 @@
         <v>47</v>
       </c>
       <c r="C50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" s="6" t="n">
         <v>1</v>
@@ -5706,46 +5706,46 @@
         <v>1</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R50" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="T50" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="V50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Z50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB50" s="6" t="n">
         <v>0</v>
@@ -5754,13 +5754,13 @@
         <v>0</v>
       </c>
       <c r="AD50" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AF50" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG50" s="6" t="n">
         <v>0</v>
@@ -5769,7 +5769,7 @@
         <v>0</v>
       </c>
       <c r="AI50" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ50" s="7" t="n">
         <v>0</v>
@@ -5780,25 +5780,25 @@
         <v>48</v>
       </c>
       <c r="C51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" s="6" t="n">
         <v>1</v>
@@ -5810,46 +5810,46 @@
         <v>1</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q51" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S51" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="U51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X51" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Y51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA51" s="6" t="n">
         <v>0</v>
@@ -5858,13 +5858,13 @@
         <v>0</v>
       </c>
       <c r="AC51" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AE51" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF51" s="6" t="n">
         <v>0</v>
@@ -5873,7 +5873,7 @@
         <v>0</v>
       </c>
       <c r="AH51" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI51" s="6" t="n">
         <v>0</v>
@@ -5887,22 +5887,22 @@
         <v>49</v>
       </c>
       <c r="C52" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" s="6" t="n">
         <v>1</v>
@@ -5914,46 +5914,46 @@
         <v>1</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R52" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="T52" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U52" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V52" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W52" s="6" t="n">
         <v>1</v>
       </c>
       <c r="X52" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y52" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z52" s="6" t="n">
         <v>0</v>
@@ -5962,13 +5962,13 @@
         <v>0</v>
       </c>
       <c r="AB52" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AD52" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE52" s="6" t="n">
         <v>0</v>
@@ -5977,7 +5977,7 @@
         <v>0</v>
       </c>
       <c r="AG52" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH52" s="6" t="n">
         <v>0</v>
@@ -5986,7 +5986,7 @@
         <v>0</v>
       </c>
       <c r="AJ52" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -5994,19 +5994,19 @@
         <v>50</v>
       </c>
       <c r="C53" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" s="6" t="n">
         <v>1</v>
@@ -6018,46 +6018,46 @@
         <v>1</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53" s="6" t="n">
         <v>0</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P53" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R53" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S53" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T53" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U53" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V53" s="6" t="n">
         <v>1</v>
       </c>
       <c r="W53" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X53" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y53" s="6" t="n">
         <v>0</v>
@@ -6066,13 +6066,13 @@
         <v>0</v>
       </c>
       <c r="AA53" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB53" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AC53" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD53" s="6" t="n">
         <v>0</v>
@@ -6081,7 +6081,7 @@
         <v>0</v>
       </c>
       <c r="AF53" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG53" s="6" t="n">
         <v>0</v>
@@ -6090,7 +6090,7 @@
         <v>0</v>
       </c>
       <c r="AI53" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ53" s="7" t="n">
         <v>0</v>
@@ -6101,16 +6101,16 @@
         <v>51</v>
       </c>
       <c r="C54" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" s="6" t="n">
         <v>1</v>
@@ -6122,46 +6122,46 @@
         <v>1</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R54" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S54" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T54" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U54" s="6" t="n">
         <v>1</v>
       </c>
       <c r="V54" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W54" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X54" s="6" t="n">
         <v>0</v>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="Z54" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AB54" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC54" s="6" t="n">
         <v>0</v>
@@ -6185,7 +6185,7 @@
         <v>0</v>
       </c>
       <c r="AE54" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF54" s="6" t="n">
         <v>0</v>
@@ -6194,7 +6194,7 @@
         <v>0</v>
       </c>
       <c r="AH54" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI54" s="6" t="n">
         <v>0</v>
@@ -6208,13 +6208,13 @@
         <v>52</v>
       </c>
       <c r="C55" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>1</v>
@@ -6226,46 +6226,46 @@
         <v>1</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q55" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S55" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T55" s="6" t="n">
         <v>1</v>
       </c>
       <c r="U55" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V55" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W55" s="6" t="n">
         <v>0</v>
@@ -6274,13 +6274,13 @@
         <v>0</v>
       </c>
       <c r="Y55" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AA55" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB55" s="6" t="n">
         <v>0</v>
@@ -6289,7 +6289,7 @@
         <v>0</v>
       </c>
       <c r="AD55" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE55" s="6" t="n">
         <v>0</v>
@@ -6298,7 +6298,7 @@
         <v>0</v>
       </c>
       <c r="AG55" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH55" s="6" t="n">
         <v>0</v>
@@ -6307,7 +6307,7 @@
         <v>0</v>
       </c>
       <c r="AJ55" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -6315,10 +6315,10 @@
         <v>53</v>
       </c>
       <c r="C56" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" s="6" t="n">
         <v>1</v>
@@ -6330,46 +6330,46 @@
         <v>1</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q56" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T56" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U56" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V56" s="6" t="n">
         <v>0</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="X56" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Z56" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA56" s="6" t="n">
         <v>0</v>
@@ -6393,7 +6393,7 @@
         <v>0</v>
       </c>
       <c r="AC56" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD56" s="6" t="n">
         <v>0</v>
@@ -6402,7 +6402,7 @@
         <v>0</v>
       </c>
       <c r="AF56" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG56" s="6" t="n">
         <v>0</v>
@@ -6411,10 +6411,10 @@
         <v>0</v>
       </c>
       <c r="AI56" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ56" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -6422,7 +6422,7 @@
         <v>54</v>
       </c>
       <c r="C57" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57" s="6" t="n">
         <v>1</v>
@@ -6434,46 +6434,46 @@
         <v>1</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q57" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R57" s="6" t="n">
         <v>1</v>
       </c>
       <c r="S57" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U57" s="6" t="n">
         <v>0</v>
@@ -6482,13 +6482,13 @@
         <v>0</v>
       </c>
       <c r="W57" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Y57" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z57" s="6" t="n">
         <v>0</v>
@@ -6497,7 +6497,7 @@
         <v>0</v>
       </c>
       <c r="AB57" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC57" s="6" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>0</v>
       </c>
       <c r="AE57" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF57" s="6" t="n">
         <v>0</v>
@@ -6515,10 +6515,10 @@
         <v>0</v>
       </c>
       <c r="AH57" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI57" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ57" s="7" t="n">
         <v>1</v>
@@ -6538,46 +6538,46 @@
         <v>1</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="6" t="n">
         <v>0</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q58" s="6" t="n">
         <v>1</v>
       </c>
       <c r="R58" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S58" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" s="6" t="n">
         <v>0</v>
@@ -6586,13 +6586,13 @@
         <v>0</v>
       </c>
       <c r="V58" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W58" s="6" t="n">
         <v>0</v>
       </c>
       <c r="X58" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y58" s="6" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
         <v>0</v>
       </c>
       <c r="AA58" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB58" s="6" t="n">
         <v>0</v>
@@ -6610,7 +6610,7 @@
         <v>0</v>
       </c>
       <c r="AD58" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE58" s="6" t="n">
         <v>0</v>
@@ -6619,10 +6619,10 @@
         <v>0</v>
       </c>
       <c r="AG58" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH58" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI58" s="6" t="n">
         <v>1</v>
@@ -6642,46 +6642,46 @@
         <v>1</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P59" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Q59" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S59" s="6" t="n">
         <v>0</v>
@@ -6690,13 +6690,13 @@
         <v>0</v>
       </c>
       <c r="U59" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V59" s="6" t="n">
         <v>0</v>
       </c>
       <c r="W59" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X59" s="6" t="n">
         <v>0</v>
@@ -6705,7 +6705,7 @@
         <v>0</v>
       </c>
       <c r="Z59" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA59" s="6" t="n">
         <v>0</v>
@@ -6714,7 +6714,7 @@
         <v>0</v>
       </c>
       <c r="AC59" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD59" s="6" t="n">
         <v>0</v>
@@ -6723,10 +6723,10 @@
         <v>0</v>
       </c>
       <c r="AF59" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG59" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH59" s="6" t="n">
         <v>1</v>
@@ -6735,7 +6735,7 @@
         <v>1</v>
       </c>
       <c r="AJ59" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -6746,46 +6746,46 @@
         <v>1</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60" s="6" t="n">
         <v>1</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q60" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" s="6" t="n">
         <v>0</v>
@@ -6794,13 +6794,13 @@
         <v>0</v>
       </c>
       <c r="T60" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U60" s="6" t="n">
         <v>0</v>
       </c>
       <c r="V60" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W60" s="6" t="n">
         <v>0</v>
@@ -6809,7 +6809,7 @@
         <v>0</v>
       </c>
       <c r="Y60" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z60" s="6" t="n">
         <v>0</v>
@@ -6818,7 +6818,7 @@
         <v>0</v>
       </c>
       <c r="AB60" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC60" s="6" t="n">
         <v>0</v>
@@ -6827,10 +6827,10 @@
         <v>0</v>
       </c>
       <c r="AE60" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF60" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG60" s="6" t="n">
         <v>1</v>
@@ -6839,7 +6839,7 @@
         <v>1</v>
       </c>
       <c r="AI60" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ60" s="7" t="n">
         <v>1</v>
@@ -6850,46 +6850,46 @@
         <v>58</v>
       </c>
       <c r="C61" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N61" s="6" t="n">
         <v>1</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q61" s="6" t="n">
         <v>0</v>
@@ -6898,13 +6898,13 @@
         <v>0</v>
       </c>
       <c r="S61" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T61" s="6" t="n">
         <v>0</v>
       </c>
       <c r="U61" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V61" s="6" t="n">
         <v>0</v>
@@ -6913,7 +6913,7 @@
         <v>0</v>
       </c>
       <c r="X61" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y61" s="6" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
         <v>0</v>
       </c>
       <c r="AA61" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB61" s="6" t="n">
         <v>0</v>
@@ -6931,10 +6931,10 @@
         <v>0</v>
       </c>
       <c r="AD61" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE61" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF61" s="6" t="n">
         <v>1</v>
@@ -6943,13 +6943,13 @@
         <v>1</v>
       </c>
       <c r="AH61" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI61" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AJ61" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -6957,43 +6957,43 @@
         <v>59</v>
       </c>
       <c r="C62" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P62" s="6" t="n">
         <v>0</v>
@@ -7002,13 +7002,13 @@
         <v>0</v>
       </c>
       <c r="R62" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S62" s="6" t="n">
         <v>0</v>
       </c>
       <c r="T62" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U62" s="6" t="n">
         <v>0</v>
@@ -7017,7 +7017,7 @@
         <v>0</v>
       </c>
       <c r="W62" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X62" s="6" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="Z62" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA62" s="6" t="n">
         <v>0</v>
@@ -7035,10 +7035,10 @@
         <v>0</v>
       </c>
       <c r="AC62" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD62" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE62" s="6" t="n">
         <v>1</v>
@@ -7047,13 +7047,13 @@
         <v>1</v>
       </c>
       <c r="AG62" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH62" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AI62" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ62" s="7" t="n">
         <v>0</v>
@@ -7064,40 +7064,40 @@
         <v>60</v>
       </c>
       <c r="C63" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E63" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="6" t="n">
         <v>1</v>
       </c>
       <c r="M63" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N63" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" s="6" t="n">
         <v>0</v>
@@ -7106,13 +7106,13 @@
         <v>0</v>
       </c>
       <c r="Q63" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R63" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S63" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T63" s="6" t="n">
         <v>0</v>
@@ -7121,7 +7121,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W63" s="6" t="n">
         <v>0</v>
@@ -7130,7 +7130,7 @@
         <v>0</v>
       </c>
       <c r="Y63" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z63" s="6" t="n">
         <v>0</v>
@@ -7139,10 +7139,10 @@
         <v>0</v>
       </c>
       <c r="AB63" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC63" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD63" s="6" t="n">
         <v>1</v>
@@ -7151,19 +7151,19 @@
         <v>1</v>
       </c>
       <c r="AF63" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG63" s="6" t="n">
         <v>1</v>
       </c>
       <c r="AH63" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI63" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AJ63" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
